--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>78981</v>
+        <v>79012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>79012</v>
+        <v>79015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,44 +776,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -855,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,35 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -776,35 +776,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -846,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,44 +892,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -776,44 +776,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -855,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,35 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>79015</v>
+        <v>79019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,32 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127241441</v>
+        <v>127241648</v>
       </c>
       <c r="B7" t="n">
-        <v>91291</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458950</v>
+        <v>458911</v>
       </c>
       <c r="R7" t="n">
-        <v>6696808</v>
+        <v>6696717</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127241648</v>
+        <v>127241441</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458911</v>
+        <v>458950</v>
       </c>
       <c r="R8" t="n">
-        <v>6696717</v>
+        <v>6696808</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>127171896</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -1213,32 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127241648</v>
+        <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458911</v>
+        <v>458950</v>
       </c>
       <c r="R7" t="n">
-        <v>6696717</v>
+        <v>6696808</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127241441</v>
+        <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458950</v>
+        <v>458911</v>
       </c>
       <c r="R8" t="n">
-        <v>6696808</v>
+        <v>6696717</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -776,35 +776,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -846,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,44 +892,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -776,44 +776,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -855,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,35 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1213,32 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127241441</v>
+        <v>127241648</v>
       </c>
       <c r="B7" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458950</v>
+        <v>458911</v>
       </c>
       <c r="R7" t="n">
-        <v>6696808</v>
+        <v>6696717</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127241648</v>
+        <v>127241441</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458911</v>
+        <v>458950</v>
       </c>
       <c r="R8" t="n">
-        <v>6696717</v>
+        <v>6696808</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75080</v>
+        <v>75082</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>79019</v>
+        <v>79021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,32 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127241441</v>
+        <v>127241648</v>
       </c>
       <c r="B7" t="n">
-        <v>91295</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458950</v>
+        <v>458911</v>
       </c>
       <c r="R7" t="n">
-        <v>6696808</v>
+        <v>6696717</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127241648</v>
+        <v>127241441</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458911</v>
+        <v>458950</v>
       </c>
       <c r="R8" t="n">
-        <v>6696717</v>
+        <v>6696808</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>127171896</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -776,35 +776,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -846,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,44 +892,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1213,32 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127241648</v>
+        <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>91297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458911</v>
+        <v>458950</v>
       </c>
       <c r="R7" t="n">
-        <v>6696717</v>
+        <v>6696808</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127241441</v>
+        <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458950</v>
+        <v>458911</v>
       </c>
       <c r="R8" t="n">
-        <v>6696808</v>
+        <v>6696717</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -776,44 +776,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -855,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,35 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75082</v>
+        <v>75085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>79021</v>
+        <v>79024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>127171896</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,35 +776,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>79641</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -846,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,44 +892,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75085</v>
+        <v>75091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>79024</v>
+        <v>79030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>127171896</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,44 +776,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -855,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,35 +883,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127241246</v>
       </c>
       <c r="B2" t="n">
-        <v>91315</v>
+        <v>91284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,35 +776,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127171546</v>
+        <v>127170334</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -846,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,44 +892,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127170334</v>
+        <v>127171546</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
@@ -962,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>127170567</v>
       </c>
       <c r="B5" t="n">
-        <v>75091</v>
+        <v>75073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127171839</v>
       </c>
       <c r="B6" t="n">
-        <v>79030</v>
+        <v>79012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127241441</v>
       </c>
       <c r="B7" t="n">
-        <v>91315</v>
+        <v>91284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>127241648</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127240660</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127240854</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>127171896</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>127242091</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>127240146</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>127240482</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127241246</v>
+        <v>127240854</v>
       </c>
       <c r="B2" t="n">
-        <v>91315</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458916</v>
+        <v>458965</v>
       </c>
       <c r="R2" t="n">
-        <v>6696826</v>
+        <v>6696767</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,48 +776,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127171546</v>
+        <v>127241246</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458939</v>
+        <v>458916</v>
       </c>
       <c r="R3" t="n">
-        <v>6696849</v>
+        <v>6696826</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -844,96 +847,81 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127170334</v>
+        <v>127241441</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458939</v>
+        <v>458950</v>
       </c>
       <c r="R4" t="n">
-        <v>6696849</v>
+        <v>6696808</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,87 +948,81 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127170567</v>
+        <v>127241648</v>
       </c>
       <c r="B5" t="n">
-        <v>75091</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458939</v>
+        <v>458911</v>
       </c>
       <c r="R5" t="n">
-        <v>6696849</v>
+        <v>6696717</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,49 +1049,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127171839</v>
+        <v>127170567</v>
       </c>
       <c r="B6" t="n">
-        <v>79030</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459023</v>
+        <v>458939</v>
       </c>
       <c r="R6" t="n">
-        <v>6696821</v>
+        <v>6696849</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1149,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1159,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,51 +1186,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127241441</v>
+        <v>127170452</v>
       </c>
       <c r="B7" t="n">
-        <v>91315</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458950</v>
+        <v>458939</v>
       </c>
       <c r="R7" t="n">
-        <v>6696808</v>
+        <v>6696849</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,40 +1254,54 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en gammal kolad stubbe</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127241648</v>
+        <v>127171896</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,40 +1309,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458911</v>
+        <v>459023</v>
       </c>
       <c r="R8" t="n">
-        <v>6696717</v>
+        <v>6696821</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,40 +1371,54 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack 3 st ringar runt tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127240660</v>
+        <v>127170334</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1453,22 +1453,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458993</v>
+        <v>458939</v>
       </c>
       <c r="R9" t="n">
-        <v>6696743</v>
+        <v>6696849</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,67 +1492,85 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127240854</v>
+        <v>127240146</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1563,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458965</v>
+        <v>458961</v>
       </c>
       <c r="R10" t="n">
-        <v>6696767</v>
+        <v>6696728</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1626,53 +1641,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127171896</v>
+        <v>127240482</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459023</v>
+        <v>458976</v>
       </c>
       <c r="R11" t="n">
-        <v>6696821</v>
+        <v>6696764</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,54 +1721,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack 3 st ringar runt tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127242091</v>
+        <v>127240660</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1781,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1790,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459001</v>
+        <v>458993</v>
       </c>
       <c r="R12" t="n">
-        <v>6696842</v>
+        <v>6696743</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1853,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127240146</v>
+        <v>127242091</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1891,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458961</v>
+        <v>459001</v>
       </c>
       <c r="R13" t="n">
-        <v>6696728</v>
+        <v>6696842</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1963,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127240482</v>
+        <v>127171839</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>79328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,49 +1982,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458976</v>
+        <v>459023</v>
       </c>
       <c r="R14" t="n">
-        <v>6696764</v>
+        <v>6696821</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,30 +2039,39 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,27 +1298,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127171896</v>
+        <v>135475351</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1327,24 +1327,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459023</v>
+        <v>459008</v>
       </c>
       <c r="R8" t="n">
-        <v>6696821</v>
+        <v>6696886</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,27 +1371,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack 3 st ringar runt tall</t>
+          <t>3 bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,54 +1396,50 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127170334</v>
+        <v>127171896</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1459,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458939</v>
+        <v>459023</v>
       </c>
       <c r="R9" t="n">
-        <v>6696849</v>
+        <v>6696821</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1483,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1493,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack 3 st ringar runt tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,57 +1525,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127240146</v>
+        <v>135475359</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458961</v>
+        <v>458952</v>
       </c>
       <c r="R10" t="n">
-        <v>6696728</v>
+        <v>6696839</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1608,12 +1598,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,7 +1617,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,57 +1635,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127240482</v>
+        <v>135475430</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458976</v>
+        <v>458948</v>
       </c>
       <c r="R11" t="n">
-        <v>6696764</v>
+        <v>6696824</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1718,12 +1708,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,7 +1727,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,57 +1745,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127240660</v>
+        <v>135475496</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458993</v>
+        <v>458959</v>
       </c>
       <c r="R12" t="n">
-        <v>6696743</v>
+        <v>6696757</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1828,12 +1818,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1837,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127242091</v>
+        <v>127170334</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1891,7 +1885,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1899,22 +1893,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459001</v>
+        <v>458939</v>
       </c>
       <c r="R13" t="n">
-        <v>6696842</v>
+        <v>6696849</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,40 +1932,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127171839</v>
+        <v>127240146</v>
       </c>
       <c r="B14" t="n">
-        <v>79328</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,37 +1982,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459023</v>
+        <v>458961</v>
       </c>
       <c r="R14" t="n">
-        <v>6696821</v>
+        <v>6696728</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,42 +2051,580 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127240482</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>458976</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6696764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127240660</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>458993</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6696743</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127242091</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>459001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6696842</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135475505</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>459039</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6696780</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127171839</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>459023</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6696821</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>malou lundin</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>malou lundin</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240854</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127241246</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127241441</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127241648</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170452</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475351</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171896</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475359</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475430</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475496</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170334</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240146</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240482</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240660</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127242091</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2518,6 +2603,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475505</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2625,8 +2715,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171839</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -1336,7 +1336,7 @@
         <v>135475351</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135475359</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135475430</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135475496</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>135475505</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -2499,7 +2499,7 @@
         <v>135475505</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1333,27 +1333,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127171896</v>
+        <v>135475351</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1362,24 +1362,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459023</v>
+        <v>459008</v>
       </c>
       <c r="R8" t="n">
-        <v>6696821</v>
+        <v>6696886</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,27 +1406,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack 3 st ringar runt tall</t>
+          <t>3 bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,59 +1431,55 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171896</t>
+          <t>https://artportalen.se/Sighting/135475351</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127170334</v>
+        <v>127171896</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458939</v>
+        <v>459023</v>
       </c>
       <c r="R9" t="n">
-        <v>6696849</v>
+        <v>6696821</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1533,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack 3 st ringar runt tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,63 +1564,59 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170334</t>
+          <t>https://artportalen.se/Sighting/127171896</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127240146</v>
+        <v>135475359</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458961</v>
+        <v>458952</v>
       </c>
       <c r="R10" t="n">
-        <v>6696728</v>
+        <v>6696839</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1653,12 +1643,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,7 +1662,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,63 +1679,59 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127240146</t>
+          <t>https://artportalen.se/Sighting/135475359</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127240482</v>
+        <v>135475430</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458976</v>
+        <v>458948</v>
       </c>
       <c r="R11" t="n">
-        <v>6696764</v>
+        <v>6696824</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1768,12 +1758,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,7 +1777,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1800,63 +1794,59 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127240482</t>
+          <t>https://artportalen.se/Sighting/135475430</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127240660</v>
+        <v>135475496</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458993</v>
+        <v>458959</v>
       </c>
       <c r="R12" t="n">
-        <v>6696743</v>
+        <v>6696757</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1883,12 +1873,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,7 +1892,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1915,13 +1909,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127240660</t>
+          <t>https://artportalen.se/Sighting/135475496</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127242091</v>
+        <v>127170334</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1951,7 +1945,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1959,22 +1953,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459001</v>
+        <v>458939</v>
       </c>
       <c r="R13" t="n">
-        <v>6696842</v>
+        <v>6696849</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,45 +1992,54 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127242091</t>
+          <t>https://artportalen.se/Sighting/127170334</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127171839</v>
+        <v>127240146</v>
       </c>
       <c r="B14" t="n">
-        <v>79328</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,37 +2047,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459023</v>
+        <v>458961</v>
       </c>
       <c r="R14" t="n">
-        <v>6696821</v>
+        <v>6696728</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,43 +2116,606 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240146</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127240482</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>458976</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6696764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240482</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127240660</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>458993</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6696743</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127240660</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127242091</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>459001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6696842</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127242091</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135475505</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>459039</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6696780</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135475505</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127171839</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>459023</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6696821</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>malou lundin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>malou lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127171839</t>
         </is>
@@ -2161,6 +2736,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -2499,7 +2499,7 @@
         <v>135475505</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 33963-2025 artfynd.xlsx
+++ b/artfynd/A 33963-2025 artfynd.xlsx
@@ -1336,7 +1336,7 @@
         <v>135475351</v>
       </c>
       <c r="B8" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135475359</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135475430</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135475496</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>135475505</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
